--- a/artfynd/A 52548-2025 artfynd.xlsx
+++ b/artfynd/A 52548-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119759349</v>
+        <v>119759350</v>
       </c>
       <c r="B2" t="n">
-        <v>91844</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3100</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>437925</v>
+        <v>437918</v>
       </c>
       <c r="R2" t="n">
-        <v>6951976</v>
+        <v>6951985</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119759347</v>
+        <v>119759346</v>
       </c>
       <c r="B3" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>438087</v>
+        <v>438076</v>
       </c>
       <c r="R3" t="n">
-        <v>6952117</v>
+        <v>6952147</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,6 +855,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,15 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119759345</v>
+        <v>119759349</v>
       </c>
       <c r="B4" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +889,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>438076</v>
+        <v>437925</v>
       </c>
       <c r="R4" t="n">
-        <v>6952147</v>
+        <v>6951976</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,15 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119759348</v>
+        <v>119759345</v>
       </c>
       <c r="B5" t="n">
-        <v>91901</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,37 +990,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5448</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Aloppsmoarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>437994</v>
+        <v>438076</v>
       </c>
       <c r="R5" t="n">
-        <v>6951937</v>
+        <v>6952147</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1080,7 +1058,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1103,15 +1080,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119759346</v>
+        <v>119759347</v>
       </c>
       <c r="B6" t="n">
-        <v>91874</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,21 +1091,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1115,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438076</v>
+        <v>438087</v>
       </c>
       <c r="R6" t="n">
-        <v>6952147</v>
+        <v>6952117</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,7 +1159,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1210,15 +1181,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119759350</v>
+        <v>119759348</v>
       </c>
       <c r="B7" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,34 +1192,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>5448</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Aloppsmoarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>437918</v>
+        <v>437994</v>
       </c>
       <c r="R7" t="n">
-        <v>6951985</v>
+        <v>6951937</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1294,6 +1263,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1309,112 +1279,6 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>119759352</v>
-      </c>
-      <c r="B8" t="n">
-        <v>91902</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>5449</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Aloppsmoarna, Jmt</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>438086</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6951969</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Härjedalen</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Vemdalen</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2024-09-08</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 52548-2025 artfynd.xlsx
+++ b/artfynd/A 52548-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119759346</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119759349</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119759345</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119759350</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1176,6 +1201,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119759347</t>
         </is>
       </c>
     </row>
@@ -1283,8 +1313,21 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119759348</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>